--- a/Capítulo02/Capítulo02/ZAP.xlsx
+++ b/Capítulo02/Capítulo02/ZAP.xlsx
@@ -1,27 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Silvia\Documents\Cursos Office 2013\PLANILHAS\PLANILHAS ATIVIDADES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://senacspedu-my.sharepoint.com/personal/yuri_smendes_senacsp_edu_br/Documents/Capítulo02/Capítulo02/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="20" documentId="11_16DDEF27C28D82276057727D3C17715D8329F8F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F512FBBA-131B-4D7A-88F8-EC1CE63031D8}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="30" windowWidth="18195" windowHeight="10035"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RELATORIO" sheetId="1" r:id="rId1"/>
     <sheet name="FERIADOS" sheetId="2" r:id="rId2"/>
     <sheet name="Plan3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="17">
   <si>
     <t>ZAP S/A - CONTROLE DE PAGAMENTOS ÀS EMPRESAS TERCEIRIZADAS</t>
   </si>
@@ -66,16 +80,22 @@
   </si>
   <si>
     <t>PERÍODO: 01/01/2013 A 31/07/2013</t>
+  </si>
+  <si>
+    <t>#=DIATRABALHOTOTAL.INTL(C6;D6;11;FERIADOS!A:A) - para saber quantos dias úteis se passaram</t>
+  </si>
+  <si>
+    <t>FUNÇÕES</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -115,8 +135,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -126,6 +154,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -157,7 +197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -180,7 +220,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -189,6 +229,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -213,9 +262,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Escritório">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -253,9 +302,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Escritório">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -290,7 +339,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -325,7 +374,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Escritório">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -498,8 +547,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H19"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.140625" customWidth="1"/>
@@ -509,9 +558,10 @@
     <col min="5" max="5" width="17" customWidth="1"/>
     <col min="6" max="6" width="11.28515625" customWidth="1"/>
     <col min="7" max="7" width="15.28515625" customWidth="1"/>
+    <col min="12" max="12" width="88.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -522,7 +572,7 @@
       <c r="F1" s="12"/>
       <c r="G1" s="12"/>
     </row>
-    <row r="2" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>14</v>
       </c>
@@ -533,7 +583,7 @@
       <c r="F2" s="13"/>
       <c r="G2" s="13"/>
     </row>
-    <row r="3" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>13</v>
       </c>
@@ -544,7 +594,12 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
     </row>
-    <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L4" s="14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>1</v>
       </c>
@@ -567,8 +622,11 @@
         <v>7</v>
       </c>
       <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="L5" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>8</v>
       </c>
@@ -584,10 +642,16 @@
       <c r="E6" s="9">
         <v>6</v>
       </c>
-      <c r="F6" s="10"/>
-      <c r="G6" s="11"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F6" s="15">
+        <f>NETWORKDAYS.INTL(C6,D6,11,FERIADOS!A:A)</f>
+        <v>47</v>
+      </c>
+      <c r="G6" s="11">
+        <f>$B$3*E6*F6</f>
+        <v>15510</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>9</v>
       </c>
@@ -603,10 +667,16 @@
       <c r="E7" s="9">
         <v>6</v>
       </c>
-      <c r="F7" s="10"/>
-      <c r="G7" s="11"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F7" s="10">
+        <f>NETWORKDAYS.INTL(C7,D7,11,FERIADOS!A:A)</f>
+        <v>28</v>
+      </c>
+      <c r="G7" s="11">
+        <f t="shared" ref="G7:G16" si="0">$B$3*E7*F7</f>
+        <v>9240</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>10</v>
       </c>
@@ -622,10 +692,16 @@
       <c r="E8" s="9">
         <v>8</v>
       </c>
-      <c r="F8" s="10"/>
-      <c r="G8" s="11"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F8" s="10">
+        <f>NETWORKDAYS.INTL(C8,D8,11,FERIADOS!A:A)</f>
+        <v>32</v>
+      </c>
+      <c r="G8" s="11">
+        <f t="shared" si="0"/>
+        <v>14080</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>9</v>
       </c>
@@ -641,10 +717,16 @@
       <c r="E9" s="9">
         <v>4</v>
       </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="11"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F9" s="10">
+        <f>NETWORKDAYS.INTL(C9,D9,11,FERIADOS!A:A)</f>
+        <v>22</v>
+      </c>
+      <c r="G9" s="11">
+        <f t="shared" si="0"/>
+        <v>4840</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>10</v>
       </c>
@@ -660,10 +742,16 @@
       <c r="E10" s="9">
         <v>4</v>
       </c>
-      <c r="F10" s="10"/>
-      <c r="G10" s="11"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F10" s="10">
+        <f>NETWORKDAYS.INTL(C10,D10,11,FERIADOS!A:A)</f>
+        <v>24</v>
+      </c>
+      <c r="G10" s="11">
+        <f t="shared" si="0"/>
+        <v>5280</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>8</v>
       </c>
@@ -679,10 +767,16 @@
       <c r="E11" s="9">
         <v>6</v>
       </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="11"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F11" s="10">
+        <f>NETWORKDAYS.INTL(C11,D11,11,FERIADOS!A:A)</f>
+        <v>7</v>
+      </c>
+      <c r="G11" s="11">
+        <f t="shared" si="0"/>
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>8</v>
       </c>
@@ -698,10 +792,16 @@
       <c r="E12" s="9">
         <v>8</v>
       </c>
-      <c r="F12" s="10"/>
-      <c r="G12" s="11"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F12" s="10">
+        <f>NETWORKDAYS.INTL(C12,D12,11,FERIADOS!A:A)</f>
+        <v>17</v>
+      </c>
+      <c r="G12" s="11">
+        <f t="shared" si="0"/>
+        <v>7480</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>10</v>
       </c>
@@ -717,10 +817,16 @@
       <c r="E13" s="9">
         <v>6</v>
       </c>
-      <c r="F13" s="10"/>
-      <c r="G13" s="11"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F13" s="10">
+        <f>NETWORKDAYS.INTL(C13,D13,11,FERIADOS!A:A)</f>
+        <v>23</v>
+      </c>
+      <c r="G13" s="11">
+        <f t="shared" si="0"/>
+        <v>7590</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>9</v>
       </c>
@@ -736,10 +842,16 @@
       <c r="E14" s="9">
         <v>4</v>
       </c>
-      <c r="F14" s="10"/>
-      <c r="G14" s="11"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F14" s="10">
+        <f>NETWORKDAYS.INTL(C14,D14,11,FERIADOS!A:A)</f>
+        <v>11</v>
+      </c>
+      <c r="G14" s="11">
+        <f t="shared" si="0"/>
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>10</v>
       </c>
@@ -755,10 +867,16 @@
       <c r="E15" s="9">
         <v>4</v>
       </c>
-      <c r="F15" s="10"/>
-      <c r="G15" s="11"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F15" s="10">
+        <f>NETWORKDAYS.INTL(C15,D15,11,FERIADOS!A:A)</f>
+        <v>12</v>
+      </c>
+      <c r="G15" s="11">
+        <f t="shared" si="0"/>
+        <v>2640</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>8</v>
       </c>
@@ -774,8 +892,14 @@
       <c r="E16" s="9">
         <v>8</v>
       </c>
-      <c r="F16" s="10"/>
-      <c r="G16" s="11"/>
+      <c r="F16" s="10">
+        <f>NETWORKDAYS.INTL(C16,D16,11,FERIADOS!A:A)</f>
+        <v>15</v>
+      </c>
+      <c r="G16" s="11">
+        <f t="shared" si="0"/>
+        <v>6600</v>
+      </c>
     </row>
     <row r="19" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D19" s="1"/>
@@ -791,7 +915,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -844,7 +968,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -853,6 +977,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100CEB2B541769F8A4991DE642272C524BB" ma:contentTypeVersion="0" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="7ae862ae5010eca0394e8ac9f072291e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="397561fba88d9dece65508bac662637b">
     <xsd:element name="properties">
@@ -966,15 +1099,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -982,13 +1106,34 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D935B0AE-9F3B-44AE-B3A6-0FBBCF855649}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A19C8D11-856D-4F41-91B1-E25632B676F2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A19C8D11-856D-4F41-91B1-E25632B676F2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D935B0AE-9F3B-44AE-B3A6-0FBBCF855649}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F148529C-ACB3-444F-BDC0-7A42C3A9EF34}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F148529C-ACB3-444F-BDC0-7A42C3A9EF34}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>